--- a/artfynd/A 60760-2019 artfynd.xlsx
+++ b/artfynd/A 60760-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121269843</v>
       </c>
       <c r="B2" t="n">
-        <v>57986</v>
+        <v>57989</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 60760-2019 artfynd.xlsx
+++ b/artfynd/A 60760-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121269843</v>
       </c>
       <c r="B2" t="n">
-        <v>57989</v>
+        <v>57992</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 60760-2019 artfynd.xlsx
+++ b/artfynd/A 60760-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121269843</v>
       </c>
       <c r="B2" t="n">
-        <v>57992</v>
+        <v>57993</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 60760-2019 artfynd.xlsx
+++ b/artfynd/A 60760-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121269843</v>
       </c>
       <c r="B2" t="n">
-        <v>57993</v>
+        <v>57994</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
